--- a/results/543-2/2_canaliculi/543-2_canaliculi_results.xlsx
+++ b/results/543-2/2_canaliculi/543-2_canaliculi_results.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -682,6 +682,441 @@
         </is>
       </c>
       <c r="G11" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>perimeter_px</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>normalised</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>222.1007</v>
+      </c>
+      <c r="D12" t="n">
+        <v>229.6934</v>
+      </c>
+      <c r="E12" t="n">
+        <v>45.067</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ring_area_r30_px2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>normalised</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>8742.1667</v>
+      </c>
+      <c r="D13" t="n">
+        <v>8905.5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1127.7798</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>px^2</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ring_area_r60_px2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>normalised</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>22189.9167</v>
+      </c>
+      <c r="D14" t="n">
+        <v>23189</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2825.3564</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>px^2</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>in_frame_fraction_r30</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>normalised</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0.9965000000000001</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.0123</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>in_frame_fraction_r60</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>normalised</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.9814000000000001</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.0596</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ring_density_r30</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>normalised</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.03474981</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.03567626</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.00762422</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>px^-1</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ring_density_r60</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>normalised</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.04342795</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.04468068</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.00529377</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>px^-1</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>roots_per_100px_perimeter</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>normalised</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>3.3871</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3.5267</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.1197</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>per 100 px</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ring_attached_length_r30_px</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>network v2</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>232.5</v>
+      </c>
+      <c r="D20" t="n">
+        <v>249</v>
+      </c>
+      <c r="E20" t="n">
+        <v>89.7689</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ring_attached_length_r60_px</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>network v2</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>572.8333</v>
+      </c>
+      <c r="D21" t="n">
+        <v>516</v>
+      </c>
+      <c r="E21" t="n">
+        <v>228.2984</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ring_length_w_r30_px</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>network v2</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>342.9959</v>
+      </c>
+      <c r="D22" t="n">
+        <v>344.528</v>
+      </c>
+      <c r="E22" t="n">
+        <v>104.4534</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ring_length_w_r60_px</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>network v2</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1096.3385</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1050.655</v>
+      </c>
+      <c r="E23" t="n">
+        <v>217.8291</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r10</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>network v2</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>8.583299999999999</v>
+      </c>
+      <c r="D24" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3.4234</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r20</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>network v2</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>12</v>
+      </c>
+      <c r="D25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3.3845</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r30</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>network v2</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>14.5833</v>
+      </c>
+      <c r="D26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="E26" t="n">
+        <v>4.5619</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
         <v>12</v>
       </c>
     </row>
@@ -696,7 +1131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -918,6 +1353,63 @@
       <c r="D11" t="inlineStr">
         <is>
           <t>px</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>field_length_density_w_per_px</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.05068186</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>px^-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>field_density_without_flagged_per_px</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.04470139</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>px^-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>field_density_in_roi_per_px</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>px^-1</t>
         </is>
       </c>
     </row>
@@ -932,7 +1424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:W13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -976,6 +1468,81 @@
           <t>mean_edge_length_px</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>perimeter_px</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ring_area_r30_px2</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ring_area_r60_px2</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>in_frame_fraction_r30</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>in_frame_fraction_r60</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ring_density_r30</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>ring_density_r60</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>roots_per_100px_perimeter</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ring_attached_length_r30_px</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ring_attached_length_r60_px</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>ring_length_w_r30_px</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>ring_length_w_r60_px</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r10</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r20</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r30</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -1002,6 +1569,51 @@
       <c r="H2" t="n">
         <v>22.1308</v>
       </c>
+      <c r="I2" t="n">
+        <v>244.4924</v>
+      </c>
+      <c r="J2" t="n">
+        <v>9510</v>
+      </c>
+      <c r="K2" t="n">
+        <v>23791</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.9843</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.0384858</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.04951452</v>
+      </c>
+      <c r="P2" t="n">
+        <v>3.6811</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>319</v>
+      </c>
+      <c r="R2" t="n">
+        <v>821</v>
+      </c>
+      <c r="S2" t="n">
+        <v>424.3036</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1357.7098</v>
+      </c>
+      <c r="U2" t="n">
+        <v>11</v>
+      </c>
+      <c r="V2" t="n">
+        <v>15</v>
+      </c>
+      <c r="W2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1028,6 +1640,51 @@
       <c r="H3" t="n">
         <v>25.1547</v>
       </c>
+      <c r="I3" t="n">
+        <v>295.1198</v>
+      </c>
+      <c r="J3" t="n">
+        <v>10519</v>
+      </c>
+      <c r="K3" t="n">
+        <v>26271</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.0484837</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.05150166</v>
+      </c>
+      <c r="P3" t="n">
+        <v>4.0661</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>373</v>
+      </c>
+      <c r="R3" t="n">
+        <v>954</v>
+      </c>
+      <c r="S3" t="n">
+        <v>578.8721</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1536.7809</v>
+      </c>
+      <c r="U3" t="n">
+        <v>15</v>
+      </c>
+      <c r="V3" t="n">
+        <v>19</v>
+      </c>
+      <c r="W3" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1054,6 +1711,51 @@
       <c r="H4" t="n">
         <v>28.8414</v>
       </c>
+      <c r="I4" t="n">
+        <v>172.8944</v>
+      </c>
+      <c r="J4" t="n">
+        <v>7548</v>
+      </c>
+      <c r="K4" t="n">
+        <v>18977</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.04186539</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.04842704</v>
+      </c>
+      <c r="P4" t="n">
+        <v>5.7839</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>246</v>
+      </c>
+      <c r="R4" t="n">
+        <v>472</v>
+      </c>
+      <c r="S4" t="n">
+        <v>346.9066</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1040.7199</v>
+      </c>
+      <c r="U4" t="n">
+        <v>10</v>
+      </c>
+      <c r="V4" t="n">
+        <v>10</v>
+      </c>
+      <c r="W4" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1782,51 @@
       <c r="H5" t="n">
         <v>19.5402</v>
       </c>
+      <c r="I5" t="n">
+        <v>232.5513</v>
+      </c>
+      <c r="J5" t="n">
+        <v>8756</v>
+      </c>
+      <c r="K5" t="n">
+        <v>18925</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.9575</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.7927999999999999</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.03483326</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.03672391</v>
+      </c>
+      <c r="P5" t="n">
+        <v>3.4401</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>266</v>
+      </c>
+      <c r="R5" t="n">
+        <v>560</v>
+      </c>
+      <c r="S5" t="n">
+        <v>342.1493</v>
+      </c>
+      <c r="T5" t="n">
+        <v>776.3402</v>
+      </c>
+      <c r="U5" t="n">
+        <v>10</v>
+      </c>
+      <c r="V5" t="n">
+        <v>13</v>
+      </c>
+      <c r="W5" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1106,6 +1853,51 @@
       <c r="H6" t="n">
         <v>28.2779</v>
       </c>
+      <c r="I6" t="n">
+        <v>154.267</v>
+      </c>
+      <c r="J6" t="n">
+        <v>7010</v>
+      </c>
+      <c r="K6" t="n">
+        <v>17818</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.03651926</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.04635762</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.5929</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>158</v>
+      </c>
+      <c r="R6" t="n">
+        <v>403</v>
+      </c>
+      <c r="S6" t="n">
+        <v>283.6934</v>
+      </c>
+      <c r="T6" t="n">
+        <v>949.3768</v>
+      </c>
+      <c r="U6" t="n">
+        <v>6</v>
+      </c>
+      <c r="V6" t="n">
+        <v>9</v>
+      </c>
+      <c r="W6" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1132,6 +1924,51 @@
       <c r="H7" t="n">
         <v>30.3348</v>
       </c>
+      <c r="I7" t="n">
+        <v>231.7645</v>
+      </c>
+      <c r="J7" t="n">
+        <v>9080</v>
+      </c>
+      <c r="K7" t="n">
+        <v>22988</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.0345815</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.03906386</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.0203</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>298</v>
+      </c>
+      <c r="R7" t="n">
+        <v>636</v>
+      </c>
+      <c r="S7" t="n">
+        <v>356.3919</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1018.0631</v>
+      </c>
+      <c r="U7" t="n">
+        <v>10</v>
+      </c>
+      <c r="V7" t="n">
+        <v>11</v>
+      </c>
+      <c r="W7" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1158,6 +1995,51 @@
       <c r="H8" t="n">
         <v>35.2664</v>
       </c>
+      <c r="I8" t="n">
+        <v>155.9239</v>
+      </c>
+      <c r="J8" t="n">
+        <v>7017</v>
+      </c>
+      <c r="K8" t="n">
+        <v>19168</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.0193815</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.03745826</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.2827</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>51</v>
+      </c>
+      <c r="R8" t="n">
+        <v>217</v>
+      </c>
+      <c r="S8" t="n">
+        <v>147.397</v>
+      </c>
+      <c r="T8" t="n">
+        <v>816.8964999999999</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
+      </c>
+      <c r="V8" t="n">
+        <v>8</v>
+      </c>
+      <c r="W8" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1184,6 +2066,51 @@
       <c r="H9" t="n">
         <v>31.1173</v>
       </c>
+      <c r="I9" t="n">
+        <v>254.2498</v>
+      </c>
+      <c r="J9" t="n">
+        <v>9429</v>
+      </c>
+      <c r="K9" t="n">
+        <v>23720</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.03786192</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.04544688</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3.9331</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>308</v>
+      </c>
+      <c r="R9" t="n">
+        <v>871</v>
+      </c>
+      <c r="S9" t="n">
+        <v>407.333</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1232.1585</v>
+      </c>
+      <c r="U9" t="n">
+        <v>11</v>
+      </c>
+      <c r="V9" t="n">
+        <v>16</v>
+      </c>
+      <c r="W9" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1210,6 +2137,51 @@
       <c r="H10" t="n">
         <v>25.8527</v>
       </c>
+      <c r="I10" t="n">
+        <v>277.0782</v>
+      </c>
+      <c r="J10" t="n">
+        <v>10094</v>
+      </c>
+      <c r="K10" t="n">
+        <v>25807</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.02476719</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.03642423</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.1655</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>159</v>
+      </c>
+      <c r="R10" t="n">
+        <v>360</v>
+      </c>
+      <c r="S10" t="n">
+        <v>267.9239</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1060.59</v>
+      </c>
+      <c r="U10" t="n">
+        <v>5</v>
+      </c>
+      <c r="V10" t="n">
+        <v>10</v>
+      </c>
+      <c r="W10" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1236,6 +2208,51 @@
       <c r="H11" t="n">
         <v>25.0376</v>
       </c>
+      <c r="I11" t="n">
+        <v>227.6224</v>
+      </c>
+      <c r="J11" t="n">
+        <v>8939</v>
+      </c>
+      <c r="K11" t="n">
+        <v>23523</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.03221837</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.04391447</v>
+      </c>
+      <c r="P11" t="n">
+        <v>3.0753</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>193</v>
+      </c>
+      <c r="R11" t="n">
+        <v>429</v>
+      </c>
+      <c r="S11" t="n">
+        <v>317.1076</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1157.1047</v>
+      </c>
+      <c r="U11" t="n">
+        <v>6</v>
+      </c>
+      <c r="V11" t="n">
+        <v>12</v>
+      </c>
+      <c r="W11" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1262,6 +2279,51 @@
       <c r="H12" t="n">
         <v>29.4597</v>
       </c>
+      <c r="I12" t="n">
+        <v>225.5219</v>
+      </c>
+      <c r="J12" t="n">
+        <v>8872</v>
+      </c>
+      <c r="K12" t="n">
+        <v>23390</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.03787196</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.04625909</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3.9907</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>252</v>
+      </c>
+      <c r="R12" t="n">
+        <v>720</v>
+      </c>
+      <c r="S12" t="n">
+        <v>369.1787</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1216.4306</v>
+      </c>
+      <c r="U12" t="n">
+        <v>9</v>
+      </c>
+      <c r="V12" t="n">
+        <v>13</v>
+      </c>
+      <c r="W12" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1287,6 +2349,51 @@
       </c>
       <c r="H13" t="n">
         <v>27.8922</v>
+      </c>
+      <c r="I13" t="n">
+        <v>193.7229</v>
+      </c>
+      <c r="J13" t="n">
+        <v>8132</v>
+      </c>
+      <c r="K13" t="n">
+        <v>21901</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.03012789</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.04004383</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3.6134</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>167</v>
+      </c>
+      <c r="R13" t="n">
+        <v>431</v>
+      </c>
+      <c r="S13" t="n">
+        <v>274.6934</v>
+      </c>
+      <c r="T13" t="n">
+        <v>993.8915</v>
+      </c>
+      <c r="U13" t="n">
+        <v>8</v>
+      </c>
+      <c r="V13" t="n">
+        <v>8</v>
+      </c>
+      <c r="W13" t="n">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
